--- a/01_用AI生成Excel/12_主管儀表板總整/全通路營運儀表板.xlsx
+++ b/01_用AI生成Excel/12_主管儀表板總整/全通路營運儀表板.xlsx
@@ -504,7 +504,9 @@
     <tableColumn id="4" name="產品類別"/>
     <tableColumn id="5" name="銷售金額"/>
     <tableColumn id="6" name="成本"/>
-    <tableColumn id="7" name="毛利"/>
+    <tableColumn id="7" name="毛利">
+      <calculatedColumnFormula>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -1152,7 +1154,7 @@
         <v>10050</v>
       </c>
       <c r="G2" s="12">
-        <f>E2-F2</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1182,7 +1184,7 @@
         <v>7560</v>
       </c>
       <c r="G3" s="12">
-        <f>E3-F3</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1212,7 +1214,7 @@
         <v>5690</v>
       </c>
       <c r="G4" s="12">
-        <f>E4-F4</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1242,7 +1244,7 @@
         <v>5120</v>
       </c>
       <c r="G5" s="12">
-        <f>E5-F5</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1274,7 @@
         <v>7290</v>
       </c>
       <c r="G6" s="12">
-        <f>E6-F6</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1304,7 @@
         <v>3160</v>
       </c>
       <c r="G7" s="12">
-        <f>E7-F7</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1332,7 +1334,7 @@
         <v>7570</v>
       </c>
       <c r="G8" s="12">
-        <f>E8-F8</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1362,7 +1364,7 @@
         <v>2030</v>
       </c>
       <c r="G9" s="12">
-        <f>E9-F9</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1392,7 +1394,7 @@
         <v>8510</v>
       </c>
       <c r="G10" s="12">
-        <f>E10-F10</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1422,7 +1424,7 @@
         <v>5790</v>
       </c>
       <c r="G11" s="12">
-        <f>E11-F11</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1452,7 +1454,7 @@
         <v>3920</v>
       </c>
       <c r="G12" s="12">
-        <f>E12-F12</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1482,7 +1484,7 @@
         <v>6450</v>
       </c>
       <c r="G13" s="12">
-        <f>E13-F13</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1512,7 +1514,7 @@
         <v>6400</v>
       </c>
       <c r="G14" s="12">
-        <f>E14-F14</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1542,7 +1544,7 @@
         <v>1440</v>
       </c>
       <c r="G15" s="12">
-        <f>E15-F15</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1572,7 +1574,7 @@
         <v>5610</v>
       </c>
       <c r="G16" s="12">
-        <f>E16-F16</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1602,7 +1604,7 @@
         <v>1250</v>
       </c>
       <c r="G17" s="12">
-        <f>E17-F17</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1632,7 +1634,7 @@
         <v>5180</v>
       </c>
       <c r="G18" s="12">
-        <f>E18-F18</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1664,7 @@
         <v>960</v>
       </c>
       <c r="G19" s="12">
-        <f>E19-F19</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1692,7 +1694,7 @@
         <v>3010</v>
       </c>
       <c r="G20" s="12">
-        <f>E20-F20</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1722,7 +1724,7 @@
         <v>4880</v>
       </c>
       <c r="G21" s="12">
-        <f>E21-F21</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1752,7 +1754,7 @@
         <v>7610</v>
       </c>
       <c r="G22" s="12">
-        <f>E22-F22</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1782,7 +1784,7 @@
         <v>5540</v>
       </c>
       <c r="G23" s="12">
-        <f>E23-F23</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1812,7 +1814,7 @@
         <v>5570</v>
       </c>
       <c r="G24" s="12">
-        <f>E24-F24</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1842,7 +1844,7 @@
         <v>6730</v>
       </c>
       <c r="G25" s="12">
-        <f>E25-F25</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1872,7 +1874,7 @@
         <v>4780</v>
       </c>
       <c r="G26" s="12">
-        <f>E26-F26</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1902,7 +1904,7 @@
         <v>7710</v>
       </c>
       <c r="G27" s="12">
-        <f>E27-F27</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1932,7 +1934,7 @@
         <v>6810</v>
       </c>
       <c r="G28" s="12">
-        <f>E28-F28</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1962,7 +1964,7 @@
         <v>6130</v>
       </c>
       <c r="G29" s="12">
-        <f>E29-F29</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -1992,7 +1994,7 @@
         <v>4100</v>
       </c>
       <c r="G30" s="12">
-        <f>E30-F30</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2022,7 +2024,7 @@
         <v>6440</v>
       </c>
       <c r="G31" s="12">
-        <f>E31-F31</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2052,7 +2054,7 @@
         <v>4630</v>
       </c>
       <c r="G32" s="12">
-        <f>E32-F32</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2082,7 +2084,7 @@
         <v>10500</v>
       </c>
       <c r="G33" s="12">
-        <f>E33-F33</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2112,7 +2114,7 @@
         <v>710</v>
       </c>
       <c r="G34" s="12">
-        <f>E34-F34</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2142,7 +2144,7 @@
         <v>3380</v>
       </c>
       <c r="G35" s="12">
-        <f>E35-F35</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2174,7 @@
         <v>3510</v>
       </c>
       <c r="G36" s="12">
-        <f>E36-F36</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2202,7 +2204,7 @@
         <v>3050</v>
       </c>
       <c r="G37" s="12">
-        <f>E37-F37</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2232,7 +2234,7 @@
         <v>3500</v>
       </c>
       <c r="G38" s="12">
-        <f>E38-F38</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2262,7 +2264,7 @@
         <v>3550</v>
       </c>
       <c r="G39" s="12">
-        <f>E39-F39</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2292,7 +2294,7 @@
         <v>5090</v>
       </c>
       <c r="G40" s="12">
-        <f>E40-F40</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2322,7 +2324,7 @@
         <v>6980</v>
       </c>
       <c r="G41" s="12">
-        <f>E41-F41</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2352,7 +2354,7 @@
         <v>10230</v>
       </c>
       <c r="G42" s="12">
-        <f>E42-F42</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2382,7 +2384,7 @@
         <v>3400</v>
       </c>
       <c r="G43" s="12">
-        <f>E43-F43</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2412,7 +2414,7 @@
         <v>3020</v>
       </c>
       <c r="G44" s="12">
-        <f>E44-F44</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2442,7 +2444,7 @@
         <v>8480</v>
       </c>
       <c r="G45" s="12">
-        <f>E45-F45</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2472,7 +2474,7 @@
         <v>3800</v>
       </c>
       <c r="G46" s="12">
-        <f>E46-F46</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2502,7 +2504,7 @@
         <v>8580</v>
       </c>
       <c r="G47" s="12">
-        <f>E47-F47</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2532,7 +2534,7 @@
         <v>5110</v>
       </c>
       <c r="G48" s="12">
-        <f>E48-F48</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2562,7 +2564,7 @@
         <v>4480</v>
       </c>
       <c r="G49" s="12">
-        <f>E49-F49</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2592,7 +2594,7 @@
         <v>2050</v>
       </c>
       <c r="G50" s="12">
-        <f>E50-F50</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2622,7 +2624,7 @@
         <v>6210</v>
       </c>
       <c r="G51" s="12">
-        <f>E51-F51</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2652,7 +2654,7 @@
         <v>8160</v>
       </c>
       <c r="G52" s="12">
-        <f>E52-F52</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2682,7 +2684,7 @@
         <v>5090</v>
       </c>
       <c r="G53" s="12">
-        <f>E53-F53</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2712,7 +2714,7 @@
         <v>5210</v>
       </c>
       <c r="G54" s="12">
-        <f>E54-F54</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2742,7 +2744,7 @@
         <v>8200</v>
       </c>
       <c r="G55" s="12">
-        <f>E55-F55</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2772,7 +2774,7 @@
         <v>2710</v>
       </c>
       <c r="G56" s="12">
-        <f>E56-F56</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2802,7 +2804,7 @@
         <v>3800</v>
       </c>
       <c r="G57" s="12">
-        <f>E57-F57</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2832,7 +2834,7 @@
         <v>800</v>
       </c>
       <c r="G58" s="12">
-        <f>E58-F58</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2862,7 +2864,7 @@
         <v>4880</v>
       </c>
       <c r="G59" s="12">
-        <f>E59-F59</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2892,7 +2894,7 @@
         <v>5220</v>
       </c>
       <c r="G60" s="12">
-        <f>E60-F60</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
@@ -2922,7 +2924,7 @@
         <v>2680</v>
       </c>
       <c r="G61" s="12">
-        <f>E61-F61</f>
+        <f>T_Sales12[[#This Row],[銷售金額]]-T_Sales12[[#This Row],[成本]]</f>
         <v/>
       </c>
     </row>
